--- a/data/nzd0023/nzd0023.xlsx
+++ b/data/nzd0023/nzd0023.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I246"/>
+  <dimension ref="A1:I247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8552,6 +8552,39 @@
         <v>367.13</v>
       </c>
       <c r="I246" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>367.89</v>
+      </c>
+      <c r="C247" t="n">
+        <v>372.52</v>
+      </c>
+      <c r="D247" t="n">
+        <v>370.21</v>
+      </c>
+      <c r="E247" t="n">
+        <v>372.7</v>
+      </c>
+      <c r="F247" t="n">
+        <v>368.26</v>
+      </c>
+      <c r="G247" t="n">
+        <v>365.4</v>
+      </c>
+      <c r="H247" t="n">
+        <v>368.15</v>
+      </c>
+      <c r="I247" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8568,7 +8601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B251"/>
+  <dimension ref="A1:B252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11081,6 +11114,16 @@
       </c>
       <c r="B251" t="n">
         <v>-0.24</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>-0.92</v>
       </c>
     </row>
   </sheetData>
@@ -11249,28 +11292,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04466766328258147</v>
+        <v>0.03980898742189387</v>
       </c>
       <c r="J2" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K2" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003064653059237865</v>
+        <v>0.002449159713975635</v>
       </c>
       <c r="M2" t="n">
-        <v>4.989281282936235</v>
+        <v>4.988819504052276</v>
       </c>
       <c r="N2" t="n">
-        <v>40.69792928124927</v>
+        <v>40.69020829925533</v>
       </c>
       <c r="O2" t="n">
-        <v>6.379492870224817</v>
+        <v>6.378887700787288</v>
       </c>
       <c r="P2" t="n">
-        <v>372.966813881217</v>
+        <v>373.0129879112736</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -11331,28 +11374,28 @@
         <v>0.0847</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05892427666105349</v>
+        <v>0.05595523681572536</v>
       </c>
       <c r="J3" t="n">
+        <v>246</v>
+      </c>
+      <c r="K3" t="n">
         <v>245</v>
       </c>
-      <c r="K3" t="n">
-        <v>244</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.007083294093104597</v>
+        <v>0.006439433479943912</v>
       </c>
       <c r="M3" t="n">
-        <v>4.178511379803143</v>
+        <v>4.176375034704456</v>
       </c>
       <c r="N3" t="n">
-        <v>30.42671153864369</v>
+        <v>30.36123674549746</v>
       </c>
       <c r="O3" t="n">
-        <v>5.516041292325837</v>
+        <v>5.510103151983405</v>
       </c>
       <c r="P3" t="n">
-        <v>374.7584807518952</v>
+        <v>374.7868153759895</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11409,28 +11452,28 @@
         <v>0.0761</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06597735286436325</v>
+        <v>0.05876021270142473</v>
       </c>
       <c r="J4" t="n">
+        <v>246</v>
+      </c>
+      <c r="K4" t="n">
         <v>245</v>
       </c>
-      <c r="K4" t="n">
-        <v>244</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.006206731135329879</v>
+        <v>0.004936451456716839</v>
       </c>
       <c r="M4" t="n">
-        <v>5.373927016310346</v>
+        <v>5.385521070269251</v>
       </c>
       <c r="N4" t="n">
-        <v>43.57243642190424</v>
+        <v>43.74152920378577</v>
       </c>
       <c r="O4" t="n">
-        <v>6.600942085937752</v>
+        <v>6.613737914658077</v>
       </c>
       <c r="P4" t="n">
-        <v>377.7302960692731</v>
+        <v>377.799171855455</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11487,28 +11530,28 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01247630712592273</v>
+        <v>-0.0177315337472691</v>
       </c>
       <c r="J5" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K5" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002440496412496884</v>
+        <v>0.0004951770216502505</v>
       </c>
       <c r="M5" t="n">
-        <v>4.874808928269101</v>
+        <v>4.878548539630008</v>
       </c>
       <c r="N5" t="n">
-        <v>39.98417188741706</v>
+        <v>40.00614788395504</v>
       </c>
       <c r="O5" t="n">
-        <v>6.323303874353743</v>
+        <v>6.325041334564941</v>
       </c>
       <c r="P5" t="n">
-        <v>379.8138140439717</v>
+        <v>379.863756661863</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11565,28 +11608,28 @@
         <v>0.0825</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03545710896508372</v>
+        <v>0.03036224021858966</v>
       </c>
       <c r="J6" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K6" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001556687824532776</v>
+        <v>0.001148749643065106</v>
       </c>
       <c r="M6" t="n">
-        <v>5.370802342465024</v>
+        <v>5.372029352291844</v>
       </c>
       <c r="N6" t="n">
-        <v>50.56251818657191</v>
+        <v>50.53040410749616</v>
       </c>
       <c r="O6" t="n">
-        <v>7.110732605475466</v>
+        <v>7.108474105424888</v>
       </c>
       <c r="P6" t="n">
-        <v>373.8884205959328</v>
+        <v>373.9368392658297</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -11643,28 +11686,28 @@
         <v>0.1304</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.003071487540003169</v>
+        <v>-0.009983620351011699</v>
       </c>
       <c r="J7" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K7" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L7" t="n">
-        <v>1.739223373431464e-05</v>
+        <v>0.0001837244545960237</v>
       </c>
       <c r="M7" t="n">
-        <v>4.41937357104372</v>
+        <v>4.434684792872849</v>
       </c>
       <c r="N7" t="n">
-        <v>34.01220331610654</v>
+        <v>34.19314673590601</v>
       </c>
       <c r="O7" t="n">
-        <v>5.831998226689248</v>
+        <v>5.847490635811742</v>
       </c>
       <c r="P7" t="n">
-        <v>374.4067941086418</v>
+        <v>374.4724829994677</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -11721,28 +11764,28 @@
         <v>0.0828</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07221692570725123</v>
+        <v>0.06658124704006607</v>
       </c>
       <c r="J8" t="n">
+        <v>246</v>
+      </c>
+      <c r="K8" t="n">
         <v>245</v>
       </c>
-      <c r="K8" t="n">
-        <v>244</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01081047952426495</v>
+        <v>0.009225078460921021</v>
       </c>
       <c r="M8" t="n">
-        <v>4.12280774989591</v>
+        <v>4.132267410038367</v>
       </c>
       <c r="N8" t="n">
-        <v>29.78220436678765</v>
+        <v>29.87164342168495</v>
       </c>
       <c r="O8" t="n">
-        <v>5.457307428282527</v>
+        <v>5.465495716006458</v>
       </c>
       <c r="P8" t="n">
-        <v>373.4573309362211</v>
+        <v>373.5111799859947</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -11780,7 +11823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I246"/>
+  <dimension ref="A1:I247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23333,6 +23376,53 @@
         </is>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>-34.81007466947493,173.16338180309972</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>-34.81079848207762,173.16355264205203</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>-34.81152481712531,173.16368073560233</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>-34.81222544545388,173.1639275228654</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>-34.812923871407804,173.16420212973722</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-34.81361759220059,173.16450739548145</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-34.81428585634506,173.16488638748376</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0023/nzd0023.xlsx
+++ b/data/nzd0023/nzd0023.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I247"/>
+  <dimension ref="A1:I248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8587,6 +8587,39 @@
       <c r="I247" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>367.55</v>
+      </c>
+      <c r="C248" t="n">
+        <v>371.43</v>
+      </c>
+      <c r="D248" t="n">
+        <v>370.67</v>
+      </c>
+      <c r="E248" t="n">
+        <v>371.9</v>
+      </c>
+      <c r="F248" t="n">
+        <v>368.95</v>
+      </c>
+      <c r="G248" t="n">
+        <v>366.65</v>
+      </c>
+      <c r="H248" t="n">
+        <v>369.53</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -8601,7 +8634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B252"/>
+  <dimension ref="A1:B253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11124,6 +11157,16 @@
       </c>
       <c r="B252" t="n">
         <v>-0.92</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -11292,28 +11335,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03980898742189387</v>
+        <v>0.03477170683075439</v>
       </c>
       <c r="J2" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K2" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002449159713975635</v>
+        <v>0.001879379405672399</v>
       </c>
       <c r="M2" t="n">
-        <v>4.988819504052276</v>
+        <v>4.988872541338474</v>
       </c>
       <c r="N2" t="n">
-        <v>40.69020829925533</v>
+        <v>40.69579809805869</v>
       </c>
       <c r="O2" t="n">
-        <v>6.378887700787288</v>
+        <v>6.379325834134724</v>
       </c>
       <c r="P2" t="n">
-        <v>373.0129879112736</v>
+        <v>373.0610980080948</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -11374,28 +11417,28 @@
         <v>0.0847</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05595523681572536</v>
+        <v>0.05219566295645923</v>
       </c>
       <c r="J3" t="n">
+        <v>247</v>
+      </c>
+      <c r="K3" t="n">
         <v>246</v>
       </c>
-      <c r="K3" t="n">
-        <v>245</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.006439433479943912</v>
+        <v>0.005642972107906097</v>
       </c>
       <c r="M3" t="n">
-        <v>4.176375034704456</v>
+        <v>4.178608950595036</v>
       </c>
       <c r="N3" t="n">
-        <v>30.36123674549746</v>
+        <v>30.33240329219669</v>
       </c>
       <c r="O3" t="n">
-        <v>5.510103151983405</v>
+        <v>5.507486113663537</v>
       </c>
       <c r="P3" t="n">
-        <v>374.7868153759895</v>
+        <v>374.8228732382602</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11452,28 +11495,28 @@
         <v>0.0761</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05876021270142473</v>
+        <v>0.05202075807062564</v>
       </c>
       <c r="J4" t="n">
+        <v>247</v>
+      </c>
+      <c r="K4" t="n">
         <v>246</v>
       </c>
-      <c r="K4" t="n">
-        <v>245</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.004936451456716839</v>
+        <v>0.003882602103371324</v>
       </c>
       <c r="M4" t="n">
-        <v>5.385521070269251</v>
+        <v>5.394853024843248</v>
       </c>
       <c r="N4" t="n">
-        <v>43.74152920378577</v>
+        <v>43.86766666344114</v>
       </c>
       <c r="O4" t="n">
-        <v>6.613737914658077</v>
+        <v>6.6232670687087</v>
       </c>
       <c r="P4" t="n">
-        <v>377.799171855455</v>
+        <v>377.8638095872709</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11530,28 +11573,28 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0177315337472691</v>
+        <v>-0.02350613373012352</v>
       </c>
       <c r="J5" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K5" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004951770216502505</v>
+        <v>0.0008732008099013866</v>
       </c>
       <c r="M5" t="n">
-        <v>4.878548539630008</v>
+        <v>4.88450438001953</v>
       </c>
       <c r="N5" t="n">
-        <v>40.00614788395504</v>
+        <v>40.06801893127785</v>
       </c>
       <c r="O5" t="n">
-        <v>6.325041334564941</v>
+        <v>6.329930404931625</v>
       </c>
       <c r="P5" t="n">
-        <v>379.863756661863</v>
+        <v>379.9189087541978</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11608,28 +11651,28 @@
         <v>0.0825</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03036224021858966</v>
+        <v>0.02588333292946297</v>
       </c>
       <c r="J6" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K6" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001148749643065106</v>
+        <v>0.0008407225033091326</v>
       </c>
       <c r="M6" t="n">
-        <v>5.372029352291844</v>
+        <v>5.370675738026805</v>
       </c>
       <c r="N6" t="n">
-        <v>50.53040410749616</v>
+        <v>50.46048694677822</v>
       </c>
       <c r="O6" t="n">
-        <v>7.108474105424888</v>
+        <v>7.103554529021244</v>
       </c>
       <c r="P6" t="n">
-        <v>373.9368392658297</v>
+        <v>373.9796164467776</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -11686,28 +11729,28 @@
         <v>0.1304</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.009983620351011699</v>
+        <v>-0.01580839634499716</v>
       </c>
       <c r="J7" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K7" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001837244545960237</v>
+        <v>0.0004617767468030332</v>
       </c>
       <c r="M7" t="n">
-        <v>4.434684792872849</v>
+        <v>4.445207777183306</v>
       </c>
       <c r="N7" t="n">
-        <v>34.19314673590601</v>
+        <v>34.28245901905321</v>
       </c>
       <c r="O7" t="n">
-        <v>5.847490635811742</v>
+        <v>5.855122459782819</v>
       </c>
       <c r="P7" t="n">
-        <v>374.4724829994677</v>
+        <v>374.5281143132215</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -11764,28 +11807,28 @@
         <v>0.0828</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06658124704006607</v>
+        <v>0.06210940682162732</v>
       </c>
       <c r="J8" t="n">
+        <v>247</v>
+      </c>
+      <c r="K8" t="n">
         <v>246</v>
       </c>
-      <c r="K8" t="n">
-        <v>245</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.009225078460921021</v>
+        <v>0.008076533803211272</v>
       </c>
       <c r="M8" t="n">
-        <v>4.132267410038367</v>
+        <v>4.136155537701764</v>
       </c>
       <c r="N8" t="n">
-        <v>29.87164342168495</v>
+        <v>29.88368654204405</v>
       </c>
       <c r="O8" t="n">
-        <v>5.465495716006458</v>
+        <v>5.466597345885652</v>
       </c>
       <c r="P8" t="n">
-        <v>373.5111799859947</v>
+        <v>373.5541211142752</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -11823,7 +11866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I247"/>
+  <dimension ref="A1:I248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23423,6 +23466,53 @@
         </is>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>-34.810075084607774,173.1633781199514</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>-34.81079999243333,173.16354086599623</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>-34.81152394439769,173.16368565251534</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>-34.812227639614925,173.16391919024744</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>-34.812921596510606,173.16420915178506</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>-34.81361328282694,173.16452002468307</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-34.8142809797598,173.1649002696404</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
